--- a/rag-mcp/data/corporate/seojun_roasters/corporate_values.xlsx
+++ b/rag-mcp/data/corporate/seojun_roasters/corporate_values.xlsx
@@ -367,7 +367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="1" max="1"/>
@@ -421,22 +421,12 @@
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
           <t>published_at</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>synthetic</t>
         </is>
       </c>
     </row>
@@ -463,7 +453,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치 — 합성</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -476,16 +466,8 @@
           <t>커피 지식·가격·직업·경제적 형편으로 고객의 인격과 방문 자격을 평가하지 않는다. 저렴한 상품을 선택하는 사람을 조롱하지 않는다.</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
+      <c r="H2" s="7" t="str"/>
       <c r="I2" s="7" t="str"/>
-      <c r="J2" s="7" t="str"/>
-      <c r="K2" s="7" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" ht="130" customHeight="1" s="1">
       <c r="A3" s="7" t="inlineStr">
@@ -510,7 +492,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치 — 합성</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -523,16 +505,8 @@
           <t>바리스타·아르바이트·배달 노동자·구직자를 하찮은 사람으로 표현하지 않는다. 특정 성별과 외모를 고객응대 능력의 기준으로 삼지 않는다.</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
+      <c r="H3" s="7" t="str"/>
       <c r="I3" s="7" t="str"/>
-      <c r="J3" s="7" t="str"/>
-      <c r="K3" s="7" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" ht="130" customHeight="1" s="1">
       <c r="A4" s="7" t="inlineStr">
@@ -557,7 +531,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치 — 합성</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -570,241 +544,203 @@
           <t>역사적 기념일·참사·고인 표현을 할인 행사나 커피의 강도를 강조하는 유머로 사용하지 않는다. 추모와 판매 유도를 구분한다.</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
+      <c r="H4" s="7" t="str"/>
       <c r="I4" s="7" t="str"/>
-      <c r="J4" s="7" t="str"/>
-      <c r="K4" s="7" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters-corporate_values-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters-corporate_values</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>corporate_values</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>서준로스터스 기업가치 — 합성</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>서준로스터스 기업가치</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>미션</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>동네 사람 누구나 부담 없이 들러 쉬어 가는 커피집을 지향한다. 커피를 잘 아는 사람이나 특정 고객만을 위한 특별한 공간보다 모두의 일상 속 쉼터가 되는 것을 목표로 한다.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters-corporate_values-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters-corporate_values</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>corporate_values</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>서준로스터스 기업가치 — 합성</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>서준로스터스 기업가치</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>핵심 가치: 지역과 함께</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>지역 농가·소상공인과의 협업과 동네 행사 참여를 중요하게 여긴다. 다른 카페나 프랜차이즈를 깎아내리는 비교보다 동네의 일상을 함께하는 이야기를 전한다.</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters-corporate_values-006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters-corporate_values</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>corporate_values</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>서준로스터스 기업가치 — 합성</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>서준로스터스 기업가치</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>브랜드 톤</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>편안하고 친근한 이웃의 말투를 사용한다. 어려운 전문 용어로 우월감을 드러내거나 커피를 모르는 고객을 가르치고 평가하려는 표현을 쓰지 않는다.</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters-corporate_values-007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters-corporate_values</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>corporate_values</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>서준로스터스 기업가치 — 합성</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>서준로스터스 기업가치</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>주요 고객</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>출근길 직장인·학생·아이와 함께 온 가족·어르신 등 동네 주민 모두를 환영한다. 나이·동반자·소비 수준으로 방문할 수 있는 사람을 나누는 메시지를 지양한다.</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters-corporate_values-008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>seojun_roasters-corporate_values</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>corporate_values</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>서준로스터스 기업가치 — 합성</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>서준로스터스 기업가치</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>운영 철학: 한 잔의 정성</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>한 잔씩 정성 들여 내리는 과정을 소중히 여긴다. 속도와 회전율 경쟁보다 잠시 기다리며 쉬어 가는 경험을 제안한다.</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>1</v>
-      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rag-mcp/data/corporate/seojun_roasters/corporate_values.xlsx
+++ b/rag-mcp/data/corporate/seojun_roasters/corporate_values.xlsx
@@ -367,7 +367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="1" max="1"/>
@@ -391,40 +391,30 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>company_id</t>
+          <t>document_type</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>document_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>section</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>content</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>published_at</t>
         </is>
@@ -438,36 +428,26 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-corporate_values</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>고객 존중</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>고객 존중</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
           <t>커피 지식·가격·직업·경제적 형편으로 고객의 인격과 방문 자격을 평가하지 않는다. 저렴한 상품을 선택하는 사람을 조롱하지 않는다.</t>
         </is>
       </c>
-      <c r="H2" s="7" t="str"/>
-      <c r="I2" s="7" t="str"/>
+      <c r="F2" s="7" t="str"/>
+      <c r="G2" s="7" t="str"/>
     </row>
     <row r="3" ht="130" customHeight="1" s="1">
       <c r="A3" s="7" t="inlineStr">
@@ -477,36 +457,26 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-corporate_values</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>직원·구직자 존중</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>직원·구직자 존중</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
           <t>바리스타·아르바이트·배달 노동자·구직자를 하찮은 사람으로 표현하지 않는다. 특정 성별과 외모를 고객응대 능력의 기준으로 삼지 않는다.</t>
         </is>
       </c>
-      <c r="H3" s="7" t="str"/>
-      <c r="I3" s="7" t="str"/>
+      <c r="F3" s="7" t="str"/>
+      <c r="G3" s="7" t="str"/>
     </row>
     <row r="4" ht="130" customHeight="1" s="1">
       <c r="A4" s="7" t="inlineStr">
@@ -516,36 +486,26 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-corporate_values</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>역사·지역사회 존중</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>역사·지역사회 존중</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
           <t>역사적 기념일·참사·고인 표현을 할인 행사나 커피의 강도를 강조하는 유머로 사용하지 않는다. 추모와 판매 유도를 구분한다.</t>
         </is>
       </c>
-      <c r="H4" s="7" t="str"/>
-      <c r="I4" s="7" t="str"/>
+      <c r="F4" s="7" t="str"/>
+      <c r="G4" s="7" t="str"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -555,36 +515,26 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-corporate_values</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>미션</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>미션</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
           <t>동네 사람 누구나 부담 없이 들러 쉬어 가는 커피집을 지향한다. 커피를 잘 아는 사람이나 특정 고객만을 위한 특별한 공간보다 모두의 일상 속 쉼터가 되는 것을 목표로 한다.</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -594,36 +544,26 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-corporate_values</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>핵심 가치: 지역과 함께</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>핵심 가치: 지역과 함께</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
           <t>지역 농가·소상공인과의 협업과 동네 행사 참여를 중요하게 여긴다. 다른 카페나 프랜차이즈를 깎아내리는 비교보다 동네의 일상을 함께하는 이야기를 전한다.</t>
         </is>
       </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -633,36 +573,26 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-corporate_values</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>브랜드 톤</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>브랜드 톤</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
           <t>편안하고 친근한 이웃의 말투를 사용한다. 어려운 전문 용어로 우월감을 드러내거나 커피를 모르는 고객을 가르치고 평가하려는 표현을 쓰지 않는다.</t>
         </is>
       </c>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -672,36 +602,26 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-corporate_values</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>주요 고객</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>주요 고객</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
           <t>출근길 직장인·학생·아이와 함께 온 가족·어르신 등 동네 주민 모두를 환영한다. 나이·동반자·소비 수준으로 방문할 수 있는 사람을 나누는 메시지를 지양한다.</t>
         </is>
       </c>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -711,36 +631,26 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-corporate_values</t>
+          <t>서준로스터스 기업가치</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>운영 철학: 한 잔의 정성</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 기업가치</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>운영 철학: 한 잔의 정성</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
           <t>한 잔씩 정성 들여 내리는 과정을 소중히 여긴다. 속도와 회전율 경쟁보다 잠시 기다리며 쉬어 가는 경험을 제안한다.</t>
         </is>
       </c>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
